--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2070-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2070-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{55AED160-AD99-46DB-B55C-F369898BA29D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C96E4BD3-DDAE-460C-8309-0304B2B6E9E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{7F6D6BB4-60BD-4FD2-811E-3CD35B76D622}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{E24B0B74-5264-4534-90B7-37F0FFC26355}"/>
   </bookViews>
   <sheets>
     <sheet name="2070-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1562,25 +1562,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94775C20-C398-4EEA-8784-8E85B7B57151}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EA3B950-8D47-4A63-931F-B79C735ACA36}">
   <dimension ref="A1:X25"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11.125" customWidth="1"/>
-    <col min="4" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="9" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1614,7 +1614,7 @@
       <c r="W1" s="32"/>
       <c r="X1" s="24"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1650,7 +1650,7 @@
       <c r="W2" s="34"/>
       <c r="X2" s="35"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1702,7 +1702,7 @@
       </c>
       <c r="X3" s="38"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1770,7 +1770,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="39">
         <v>2025</v>
       </c>
@@ -1842,7 +1842,7 @@
         <v>1.33</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1916,7 +1916,7 @@
         <v>1.33</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="41">
         <v>2024</v>
       </c>
@@ -1988,7 +1988,7 @@
         <v>4.58</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>29</v>
       </c>
@@ -2062,7 +2062,7 @@
         <v>1.33</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2136,7 +2136,7 @@
         <v>3.25</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="39">
         <v>2023</v>
       </c>
@@ -2208,7 +2208,7 @@
         <v>4.87</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>29</v>
       </c>
@@ -2282,7 +2282,7 @@
         <v>4.87</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>29</v>
       </c>
@@ -2356,7 +2356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="41">
         <v>2022</v>
       </c>
@@ -2428,7 +2428,7 @@
         <v>5.29</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>29</v>
       </c>
@@ -2502,7 +2502,7 @@
         <v>5.29</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>29</v>
       </c>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="39">
         <v>2021</v>
       </c>
@@ -2648,7 +2648,7 @@
         <v>5.39</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="41">
         <v>2020</v>
       </c>
@@ -2720,7 +2720,7 @@
         <v>3.91</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="39">
         <v>2019</v>
       </c>
@@ -2792,7 +2792,7 @@
         <v>4.54</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="41">
         <v>2018</v>
       </c>
@@ -2864,7 +2864,7 @@
         <v>7.41</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="39">
         <v>2017</v>
       </c>
@@ -2936,7 +2936,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="43">
         <v>2016</v>
       </c>
@@ -3008,7 +3008,7 @@
         <v>4.88</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="45"/>
       <c r="B22" s="46"/>
       <c r="C22" s="20" t="s">
@@ -3036,7 +3036,7 @@
       <c r="W22" s="54"/>
       <c r="X22" s="48"/>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="55">
         <v>2015</v>
       </c>
@@ -3108,7 +3108,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="57"/>
       <c r="B24" s="58"/>
       <c r="C24" s="22" t="s">
@@ -3136,7 +3136,7 @@
       <c r="W24" s="64"/>
       <c r="X24" s="60"/>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="41" t="s">
         <v>49</v>
       </c>
